--- a/docs/req_control_actions.xlsx
+++ b/docs/req_control_actions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действия системы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Действия системы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Действия системы'!$A$1:$C$46</definedName>
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1089,36 +1089,36 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>ЗАДАЧИ</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ЗАДАЧИ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Обновить задачу</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Обновляемые поля title, description, readiness процент готовности, status из справочника</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ЗАДАЧИ</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Переместить задачу в другую стори</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>story_id обновлён</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>АНАЛИТИКА</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Получить сводку по проекту</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Счётчики эпик/стори/задач, общий % готовности</t>
         </is>
       </c>
     </row>
@@ -1128,14 +1128,14 @@
           <t>АНАЛИТИКА</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Получить прогресс эпика</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>AVG readiness задач, кол-во завершённых сторей</t>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Получить сводку по проекту</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Счётчики эпик/стори/задач, общий % готовности</t>
         </is>
       </c>
     </row>
@@ -1145,14 +1145,14 @@
           <t>АНАЛИТИКА</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Получить прогресс стори</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>AVG readiness задач стори</t>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Получить прогресс эпика</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>AVG readiness задач, кол-во завершённых сторей</t>
         </is>
       </c>
     </row>
@@ -1162,14 +1162,14 @@
           <t>АНАЛИТИКА</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Gap-анализ: незакрытые требования</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>ФТ/БТ без привязанных выполненных задач</t>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Получить прогресс стори</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>AVG readiness задач стори</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1179,14 @@
           <t>АНАЛИТИКА</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Получить задачи «На уточнении»</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Список задач в статусе 4 по всему проекту</t>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Gap-анализ: незакрытые требования</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>ФТ/БТ без привязанных выполненных задач</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1196,14 @@
           <t>АНАЛИТИКА</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Получить сроки задачи</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>created_at, updated_at, статус, readiness</t>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Получить задачи «На уточнении»</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Список задач в статусе 4 по всему проекту</t>
         </is>
       </c>
     </row>
@@ -1213,31 +1213,31 @@
           <t>АНАЛИТИКА</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Получить сроки задачи</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>created_at, updated_at, статус, readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>АНАЛИТИКА</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Получить историю изменений сущности</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Лог updated_at + предыдущие значения полей</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>ВЕРСИИ</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Создать новую версию требования</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Запись с version_num, ссылка на предыдущую</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1247,14 @@
           <t>ВЕРСИИ</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Получить все версии требования</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Список: version_num, дата, описание изменений</t>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Создать новую версию требования</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Запись с version_num, ссылка на предыдущую</t>
         </is>
       </c>
     </row>
@@ -1264,14 +1264,14 @@
           <t>ВЕРСИИ</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Сравнить две версии требования</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Diff: добавлено / изменено / удалено</t>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Получить все версии требования</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Список: version_num, дата, описание изменений</t>
         </is>
       </c>
     </row>
@@ -1281,31 +1281,31 @@
           <t>ВЕРСИИ</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Сравнить две версии требования</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Diff: добавлено / изменено / удалено</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>ВЕРСИИ</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Откатить требование к версии N</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Активная версия изменена, старая → archived</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>СИСТЕМА</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Получить список статусов задач</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Все записи core.statuses: id, name</t>
         </is>
       </c>
     </row>
@@ -1315,14 +1315,14 @@
           <t>СИСТЕМА</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Получить список типов сущностей</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Все записи core.entity_types: id, type</t>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Получить список статусов задач</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Все записи core.statuses: id, name</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,29 @@
           <t>СИСТЕМА</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Получить список типов сущностей</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Все записи core.entity_types: id, type</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>СИСТЕМА</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Получить схему базы данных</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Таблицы, поля, типы данных, FK-связи</t>
         </is>
